--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104295286</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146435</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146444</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148796</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146197</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148827</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724086</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724091</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146177</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146189</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146190</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146328</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146336</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146391</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146409</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146412</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146446</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148798</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2992,6 +3107,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148799</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3089,6 +3209,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148813</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3196,6 +3321,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146469</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3303,6 +3433,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724081</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3400,6 +3535,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998695</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3497,6 +3637,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998709</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3594,6 +3739,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998710</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3701,6 +3851,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724087</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3808,6 +3963,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724092</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3905,6 +4065,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104295288</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4006,6 +4171,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146164</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4107,6 +4277,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146186</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4208,6 +4383,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146322</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4309,6 +4489,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146399</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4410,6 +4595,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146406</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4511,6 +4701,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146424</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4612,6 +4807,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146428</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4713,6 +4913,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146450</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4814,6 +5019,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146453</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4911,6 +5121,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148800</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5008,6 +5223,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148808</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5105,6 +5325,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148812</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5202,6 +5427,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148819</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5299,6 +5529,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148820</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5396,6 +5631,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148821</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5493,6 +5733,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148822</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5590,6 +5835,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148823</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5699,6 +5949,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146349</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5808,6 +6063,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146459</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5909,6 +6169,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146463</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6006,6 +6271,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104295289</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6107,6 +6377,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146270</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6213,6 +6488,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146320</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6314,6 +6594,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146471</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6411,6 +6696,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148793</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6508,6 +6798,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998697</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6605,6 +6900,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998707</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6706,6 +7006,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146426</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6807,6 +7112,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146159</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6914,6 +7224,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724072</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7021,6 +7336,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724082</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7118,6 +7438,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148817</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7225,6 +7550,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146422</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7330,6 +7660,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146173</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7427,6 +7762,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998712</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7542,6 +7882,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146479</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7639,6 +7984,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148801</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7736,6 +8086,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148804</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7833,6 +8188,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148805</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7930,6 +8290,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148806</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8027,6 +8392,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148825</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8124,6 +8494,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148828</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8243,6 +8618,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101981516</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8340,6 +8720,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998694</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8437,6 +8822,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998708</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8544,6 +8934,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724073</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8651,6 +9046,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724077</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8758,6 +9158,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724088</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8855,6 +9260,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148794</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8952,6 +9362,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148795</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9049,6 +9464,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148797</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9146,6 +9566,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148814</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9243,6 +9668,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148816</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9340,6 +9770,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148818</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9441,6 +9876,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146364</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9548,6 +9988,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724084</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9649,6 +10094,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146369</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9746,6 +10196,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148811</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9847,6 +10302,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146385</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9956,6 +10416,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146376</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10053,6 +10518,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998713</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10160,6 +10630,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724071</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10267,6 +10742,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79724079</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10377,6 +10857,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146355</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10487,6 +10972,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146360</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10584,6 +11074,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148809</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10681,6 +11176,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148810</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10778,6 +11278,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148829</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10888,8 +11393,116 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121344480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7668,10 +7668,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66998712</v>
+        <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99022</v>
+        <v>99330</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7679,37 +7679,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>Återkommer, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442638</v>
+        <v>442571</v>
       </c>
       <c r="R68" t="n">
-        <v>6631052</v>
+        <v>6631358</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7733,12 +7742,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>I bankslänt på södra sidan vägen. 1 meter ifrån varandra.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7753,74 +7767,66 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66998712</t>
+          <t>https://artportalen.se/Sighting/136438438</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120146479</v>
+        <v>66998712</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442651</v>
+        <v>442638</v>
       </c>
       <c r="R69" t="n">
-        <v>6631343</v>
+        <v>6631052</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7847,17 +7853,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2 blomstänglar.</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7866,31 +7867,30 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146479</t>
+          <t>https://artportalen.se/Sighting/66998712</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120148801</v>
+        <v>120146479</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -7918,17 +7918,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442549</v>
+        <v>442651</v>
       </c>
       <c r="R70" t="n">
-        <v>6631204</v>
+        <v>6631343</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,36 +7975,42 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2 blomstänglar.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148801</t>
+          <t>https://artportalen.se/Sighting/120146479</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120148804</v>
+        <v>120148801</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8027,10 +8045,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442566</v>
+        <v>442549</v>
       </c>
       <c r="R71" t="n">
-        <v>6631166</v>
+        <v>6631204</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8088,13 +8106,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148804</t>
+          <t>https://artportalen.se/Sighting/120148801</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120148805</v>
+        <v>120148804</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8129,10 +8147,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442575</v>
+        <v>442566</v>
       </c>
       <c r="R72" t="n">
-        <v>6631144</v>
+        <v>6631166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8190,13 +8208,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148805</t>
+          <t>https://artportalen.se/Sighting/120148804</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120148806</v>
+        <v>120148805</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8231,10 +8249,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442543</v>
+        <v>442575</v>
       </c>
       <c r="R73" t="n">
-        <v>6631132</v>
+        <v>6631144</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8292,13 +8310,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148806</t>
+          <t>https://artportalen.se/Sighting/120148805</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120148825</v>
+        <v>120148806</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8333,10 +8351,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442558</v>
+        <v>442543</v>
       </c>
       <c r="R74" t="n">
-        <v>6631161</v>
+        <v>6631132</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8394,13 +8412,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148825</t>
+          <t>https://artportalen.se/Sighting/120148806</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120148828</v>
+        <v>120148825</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8435,10 +8453,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442659</v>
+        <v>442558</v>
       </c>
       <c r="R75" t="n">
-        <v>6631348</v>
+        <v>6631161</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8496,70 +8514,54 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148828</t>
+          <t>https://artportalen.se/Sighting/120148825</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>101981516</v>
+        <v>120148828</v>
       </c>
       <c r="B76" t="n">
-        <v>102464</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221343</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442543</v>
+        <v>442659</v>
       </c>
       <c r="R76" t="n">
-        <v>6631330</v>
+        <v>6631348</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8583,17 +8585,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis, för mycket bromsar för att räkna alla.</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8602,72 +8599,87 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101981516</t>
+          <t>https://artportalen.se/Sighting/120148828</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66998694</v>
+        <v>101981516</v>
       </c>
       <c r="B77" t="n">
-        <v>80392</v>
+        <v>102464</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>221343</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442620</v>
+        <v>442543</v>
       </c>
       <c r="R77" t="n">
-        <v>6630942</v>
+        <v>6631330</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8691,12 +8703,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis, för mycket bromsar för att räkna alla.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8705,71 +8722,81 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66998694</t>
+          <t>https://artportalen.se/Sighting/101981516</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66998708</v>
+        <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>80392</v>
+        <v>102680</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>221343</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>Flymossen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442566</v>
+        <v>442579</v>
       </c>
       <c r="R78" t="n">
-        <v>6630751</v>
+        <v>6631365</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,12 +8820,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I ytterslänt på norra sidan vägen.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8813,65 +8845,78 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66998708</t>
+          <t>https://artportalen.se/Sighting/136438441</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>79724073</v>
+        <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>80392</v>
+        <v>102680</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>221343</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>Flymossen, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442598</v>
+        <v>442596</v>
       </c>
       <c r="R79" t="n">
-        <v>6630959</v>
+        <v>6631370</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8895,22 +8940,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I ytterslänt på norra sidan vägen. Svårt att avgöra plantor från stjälkar så räknade möjligtvis något lågt.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8925,24 +8965,28 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724073</t>
+          <t>https://artportalen.se/Sighting/136438443</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79724077</v>
+        <v>66998694</v>
       </c>
       <c r="B80" t="n">
         <v>80392</v>
@@ -8977,10 +9021,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442510</v>
+        <v>442620</v>
       </c>
       <c r="R80" t="n">
-        <v>6630845</v>
+        <v>6630942</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9007,22 +9051,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9048,13 +9082,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724077</t>
+          <t>https://artportalen.se/Sighting/66998694</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>79724088</v>
+        <v>66998708</v>
       </c>
       <c r="B81" t="n">
         <v>80392</v>
@@ -9089,10 +9123,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442589</v>
+        <v>442566</v>
       </c>
       <c r="R81" t="n">
-        <v>6630889</v>
+        <v>6630751</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9119,22 +9153,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9160,13 +9184,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724088</t>
+          <t>https://artportalen.se/Sighting/66998708</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120148794</v>
+        <v>79724073</v>
       </c>
       <c r="B82" t="n">
         <v>80392</v>
@@ -9197,14 +9221,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>442617</v>
+        <v>442598</v>
       </c>
       <c r="R82" t="n">
-        <v>6631287</v>
+        <v>6630959</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9231,12 +9255,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9262,13 +9296,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148794</t>
+          <t>https://artportalen.se/Sighting/79724073</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120148795</v>
+        <v>79724077</v>
       </c>
       <c r="B83" t="n">
         <v>80392</v>
@@ -9299,14 +9333,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>442638</v>
+        <v>442510</v>
       </c>
       <c r="R83" t="n">
-        <v>6631238</v>
+        <v>6630845</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9333,12 +9367,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9364,13 +9408,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148795</t>
+          <t>https://artportalen.se/Sighting/79724077</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120148797</v>
+        <v>79724088</v>
       </c>
       <c r="B84" t="n">
         <v>80392</v>
@@ -9401,14 +9445,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442626</v>
+        <v>442589</v>
       </c>
       <c r="R84" t="n">
-        <v>6631318</v>
+        <v>6630889</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9435,12 +9479,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9466,13 +9520,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148797</t>
+          <t>https://artportalen.se/Sighting/79724088</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120148814</v>
+        <v>120148794</v>
       </c>
       <c r="B85" t="n">
         <v>80392</v>
@@ -9507,10 +9561,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442595</v>
+        <v>442617</v>
       </c>
       <c r="R85" t="n">
-        <v>6630897</v>
+        <v>6631287</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9568,13 +9622,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148814</t>
+          <t>https://artportalen.se/Sighting/120148794</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120148816</v>
+        <v>120148795</v>
       </c>
       <c r="B86" t="n">
         <v>80392</v>
@@ -9609,10 +9663,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442597</v>
+        <v>442638</v>
       </c>
       <c r="R86" t="n">
-        <v>6630801</v>
+        <v>6631238</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9670,13 +9724,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148816</t>
+          <t>https://artportalen.se/Sighting/120148795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120148818</v>
+        <v>120148797</v>
       </c>
       <c r="B87" t="n">
         <v>80392</v>
@@ -9711,10 +9765,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>442520</v>
+        <v>442626</v>
       </c>
       <c r="R87" t="n">
-        <v>6630838</v>
+        <v>6631318</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9772,54 +9826,51 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148818</t>
+          <t>https://artportalen.se/Sighting/120148797</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120146364</v>
+        <v>120148814</v>
       </c>
       <c r="B88" t="n">
-        <v>83299</v>
+        <v>80392</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>442775</v>
+        <v>442595</v>
       </c>
       <c r="R88" t="n">
-        <v>6631023</v>
+        <v>6630897</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9860,69 +9911,68 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146364</t>
+          <t>https://artportalen.se/Sighting/120148814</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>79724084</v>
+        <v>120148816</v>
       </c>
       <c r="B89" t="n">
-        <v>91909</v>
+        <v>80392</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>442718</v>
+        <v>442597</v>
       </c>
       <c r="R89" t="n">
-        <v>6631065</v>
+        <v>6630801</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9949,22 +9999,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9990,54 +10030,51 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724084</t>
+          <t>https://artportalen.se/Sighting/120148816</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120146369</v>
+        <v>120148818</v>
       </c>
       <c r="B90" t="n">
-        <v>91909</v>
+        <v>80392</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>442780</v>
+        <v>442520</v>
       </c>
       <c r="R90" t="n">
-        <v>6630987</v>
+        <v>6630838</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10078,69 +10115,71 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146369</t>
+          <t>https://artportalen.se/Sighting/120148818</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120148811</v>
+        <v>120146364</v>
       </c>
       <c r="B91" t="n">
-        <v>92632</v>
+        <v>83299</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>442771</v>
+        <v>442775</v>
       </c>
       <c r="R91" t="n">
-        <v>6631032</v>
+        <v>6631023</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10181,71 +10220,69 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148811</t>
+          <t>https://artportalen.se/Sighting/120146364</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120146385</v>
+        <v>79724084</v>
       </c>
       <c r="B92" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442809</v>
+        <v>442718</v>
       </c>
       <c r="R92" t="n">
-        <v>6631004</v>
+        <v>6631065</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10272,12 +10309,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10286,68 +10333,59 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146385</t>
+          <t>https://artportalen.se/Sighting/79724084</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120146376</v>
+        <v>120146369</v>
       </c>
       <c r="B93" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -10356,10 +10394,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>442821</v>
+        <v>442780</v>
       </c>
       <c r="R93" t="n">
-        <v>6631011</v>
+        <v>6630987</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10418,51 +10456,51 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146376</t>
+          <t>https://artportalen.se/Sighting/120146369</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>66998713</v>
+        <v>120148811</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>92632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Milkullen, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>442734</v>
+        <v>442771</v>
       </c>
       <c r="R94" t="n">
-        <v>6631331</v>
+        <v>6631032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10489,12 +10527,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10520,51 +10558,54 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66998713</t>
+          <t>https://artportalen.se/Sighting/120148811</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>79724071</v>
+        <v>120146385</v>
       </c>
       <c r="B95" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>442745</v>
+        <v>442809</v>
       </c>
       <c r="R95" t="n">
-        <v>6631026</v>
+        <v>6631004</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10591,22 +10632,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10615,33 +10646,34 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724071</t>
+          <t>https://artportalen.se/Sighting/120146385</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>79724079</v>
+        <v>120146376</v>
       </c>
       <c r="B96" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10649,34 +10681,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>442707</v>
+        <v>442821</v>
       </c>
       <c r="R96" t="n">
-        <v>6631055</v>
+        <v>6631011</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10703,22 +10746,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10727,30 +10760,31 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79724079</t>
+          <t>https://artportalen.se/Sighting/120146376</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120146355</v>
+        <v>66998713</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -10778,29 +10812,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>442736</v>
+        <v>442734</v>
       </c>
       <c r="R97" t="n">
-        <v>6631051</v>
+        <v>6631331</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10827,12 +10849,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10841,31 +10863,30 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146355</t>
+          <t>https://artportalen.se/Sighting/66998713</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120146360</v>
+        <v>79724071</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -10893,29 +10914,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>442758</v>
+        <v>442745</v>
       </c>
       <c r="R98" t="n">
-        <v>6631033</v>
+        <v>6631026</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10942,12 +10951,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10956,31 +10975,30 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120146360</t>
+          <t>https://artportalen.se/Sighting/79724071</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120148809</v>
+        <v>79724079</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -11011,14 +11029,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>442724</v>
+        <v>442707</v>
       </c>
       <c r="R99" t="n">
-        <v>6631071</v>
+        <v>6631055</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11045,12 +11063,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11076,13 +11104,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148809</t>
+          <t>https://artportalen.se/Sighting/79724079</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120148810</v>
+        <v>120146355</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -11110,17 +11138,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>442725</v>
+        <v>442736</v>
       </c>
       <c r="R100" t="n">
-        <v>6631068</v>
+        <v>6631051</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11161,30 +11201,31 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148810</t>
+          <t>https://artportalen.se/Sighting/120146355</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120148829</v>
+        <v>120146360</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -11212,17 +11253,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>V om Milkullen, Vrm</t>
+          <t>Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>442705</v>
+        <v>442758</v>
       </c>
       <c r="R101" t="n">
-        <v>6631360</v>
+        <v>6631033</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11263,30 +11316,31 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148829</t>
+          <t>https://artportalen.se/Sighting/120146360</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121344480</v>
+        <v>120148809</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -11314,21 +11368,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Milkullen, VNV om, Vrm</t>
+          <t>V om Milkullen, Vrm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>442707</v>
+        <v>442724</v>
       </c>
       <c r="R102" t="n">
-        <v>6631056</v>
+        <v>6631071</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11353,11 +11403,6 @@
           <t>Färnebo</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>S-Fil-0183</t>
-        </is>
-      </c>
       <c r="Y102" t="inlineStr">
         <is>
           <t>2024-10-01</t>
@@ -11380,20 +11425,335 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148809</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120148810</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>V om Milkullen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>442725</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6631068</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148810</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120148829</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>V om Milkullen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>442705</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6631360</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148829</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121344480</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Milkullen, VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>442707</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6631056</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>S-Fil-0183</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
+      <c r="AX105" t="inlineStr">
         <is>
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr">
+      <c r="AY105" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
+      <c r="AZ105" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121344480</t>
         </is>
@@ -11502,6 +11862,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99330</v>
+        <v>99343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102680</v>
+        <v>102693</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102680</v>
+        <v>102693</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102693</v>
+        <v>102694</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102693</v>
+        <v>102694</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
